--- a/AtchisonRegime/Outputs/Brazil/MSCI_Europe/df_regSummary_MSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/Brazil/MSCI_Europe/df_regSummary_MSCI_Europe.xlsx
@@ -545,7 +545,7 @@
         <v>11.6865661939146</v>
       </c>
       <c r="K2" t="n">
-        <v>33.65079365079365</v>
+        <v>33.54430379746836</v>
       </c>
       <c r="L2" t="n">
         <v>10</v>
@@ -603,7 +603,7 @@
         <v>9.151803599435841</v>
       </c>
       <c r="K3" t="n">
-        <v>18.41269841269841</v>
+        <v>18.35443037974684</v>
       </c>
       <c r="L3" t="n">
         <v>9</v>
@@ -646,13 +646,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>1.018506994431313</v>
+        <v>1.033032182677109</v>
       </c>
       <c r="H4" t="n">
-        <v>2.994703775813029</v>
+        <v>2.969344463410093</v>
       </c>
       <c r="I4" t="n">
         <v>-6.01259591566895</v>
@@ -661,16 +661,16 @@
         <v>6.22329041882997</v>
       </c>
       <c r="K4" t="n">
-        <v>17.46031746031746</v>
+        <v>17.72151898734177</v>
       </c>
       <c r="L4" t="n">
         <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>4.583333333333333</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04983897140688512</v>
+        <v>0.05158122711572511</v>
       </c>
       <c r="O4" t="n">
         <v>-0.08238334306553563</v>
@@ -719,7 +719,7 @@
         <v>9.70751728527032</v>
       </c>
       <c r="K5" t="n">
-        <v>30.47619047619048</v>
+        <v>30.37974683544304</v>
       </c>
       <c r="L5" t="n">
         <v>10</v>
